--- a/data/trans_orig/Q45B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>38085</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27194</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51098</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>52244</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>38736</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>68923</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38085</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27413</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51935</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>52244</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>39841</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>70490</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>445634</t>
+          <t>445957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>464290</t>
+          <t>464435</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251741</t>
+          <t>251806</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>276605</t>
+          <t>276864</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>703967</t>
+          <t>703943</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>734530</t>
+          <t>736998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>47518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77332</t>
+          <t>78640</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52066</t>
+          <t>51450</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83494</t>
+          <t>83792</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>358013</t>
+          <t>358891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366042</t>
+          <t>366056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287029</t>
+          <t>286596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316499</t>
+          <t>317557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>646970</t>
+          <t>648425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>679637</t>
+          <t>680363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>521608</t>
+          <t>522298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>535762</t>
+          <t>535886</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139593</t>
+          <t>140143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155594</t>
+          <t>156279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667742</t>
+          <t>667687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>688445</t>
+          <t>688376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44092</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72570</t>
+          <t>75335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58897</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92945</t>
+          <t>91884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1207562</t>
+          <t>1204406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1225232</t>
+          <t>1224755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640804</t>
+          <t>638003</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>668914</t>
+          <t>668169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1853528</t>
+          <t>1854937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1889111</t>
+          <t>1888583</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -2556,97 +2556,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38710</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47803</t>
+          <t>46734</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>335608</t>
+          <t>335601</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>347531</t>
+          <t>347032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>530042</t>
+          <t>529870</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>551379</t>
+          <t>550960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>871504</t>
+          <t>872573</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>895519</t>
+          <t>896009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -3012,97 +3012,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65134</t>
+          <t>63116</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>39903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68353</t>
+          <t>67868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>289015</t>
+          <t>288404</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297203</t>
+          <t>297180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1183626</t>
+          <t>1185644</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1211296</t>
+          <t>1212349</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1478607</t>
+          <t>1479092</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1507204</t>
+          <t>1507057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20499</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35032</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>42284</t>
+          <t>42311</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72595</t>
+          <t>72492</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>222784</t>
+          <t>218753</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>281547</t>
+          <t>279406</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271369</t>
+          <t>274090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>340061</t>
+          <t>344682</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3185064</t>
+          <t>3184979</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3218792</t>
+          <t>3218652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3082847</t>
+          <t>3084917</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3143698</t>
+          <t>3146755</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6282210</t>
+          <t>6278516</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6354685</t>
+          <t>6354629</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>27099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>27445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>53547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>40422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70627</t>
+          <t>72828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>408872</t>
+          <t>408966</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>427443</t>
+          <t>427262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253781</t>
+          <t>253250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>280230</t>
+          <t>280880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>671694</t>
+          <t>670366</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>704508</t>
+          <t>704351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32907</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59994</t>
+          <t>57675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39421</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69101</t>
+          <t>71317</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>398709</t>
+          <t>398781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>412557</t>
+          <t>412565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>272331</t>
+          <t>274094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>300240</t>
+          <t>300827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679608</t>
+          <t>677715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>710693</t>
+          <t>709206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>23700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30369</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47665</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>597791</t>
+          <t>598294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>614332</t>
+          <t>615036</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>220891</t>
+          <t>221145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241568</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>825706</t>
+          <t>823409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>853797</t>
+          <t>852399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45364</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76161</t>
+          <t>74805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68668</t>
+          <t>70168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105352</t>
+          <t>106653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1108718</t>
+          <t>1109382</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1132824</t>
+          <t>1132076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>684065</t>
+          <t>685201</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>715714</t>
+          <t>715519</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1802491</t>
+          <t>1802416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1841756</t>
+          <t>1839361</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>33722</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>40575</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>498154</t>
+          <t>497658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>508537</t>
+          <t>508525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>718110</t>
+          <t>717521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>738373</t>
+          <t>738389</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1221932</t>
+          <t>1220358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1245182</t>
+          <t>1244667</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34086</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60245</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39472</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>68643</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>254190</t>
+          <t>254355</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264588</t>
+          <t>264606</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1037945</t>
+          <t>1039086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1066687</t>
+          <t>1066474</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1295376</t>
+          <t>1296411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1327141</t>
+          <t>1328195</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22885</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>47376</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56166</t>
+          <t>55620</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>62263</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>97541</t>
+          <t>98089</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>202353</t>
+          <t>198592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>259544</t>
+          <t>261476</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>273873</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>341242</t>
+          <t>341665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3303040</t>
+          <t>3302293</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3339942</t>
+          <t>3339306</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3243599</t>
+          <t>3238471</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3304692</t>
+          <t>3307382</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6561626</t>
+          <t>6559894</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6635104</t>
+          <t>6634171</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,97 +7584,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7041</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2061</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7323</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>7767</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8140</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>419735</t>
+          <t>419707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>428072</t>
+          <t>428085</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>322104</t>
+          <t>323459</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>338086</t>
+          <t>339173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>746803</t>
+          <t>747325</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>764484</t>
+          <t>764570</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362951</t>
+          <t>362982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>345983</t>
+          <t>346290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>361475</t>
+          <t>361408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>713713</t>
+          <t>714426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>730104</t>
+          <t>730329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>19857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>510641</t>
+          <t>510801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>519727</t>
+          <t>519803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148695</t>
+          <t>147818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159809</t>
+          <t>159774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662436</t>
+          <t>663236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>677584</t>
+          <t>678076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30939</t>
+          <t>30441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57115</t>
+          <t>54799</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40609</t>
+          <t>40680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68386</t>
+          <t>68865</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1126570</t>
+          <t>1128439</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1141533</t>
+          <t>1141867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>758234</t>
+          <t>759079</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>785607</t>
+          <t>785308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1891795</t>
+          <t>1893308</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1922122</t>
+          <t>1923050</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,82 +9536,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>13434</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>7021</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>22216</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>20412</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>12760</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>31181</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>13434</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>7678</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>22139</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>20412</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>13030</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>31417</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>604136</t>
+          <t>604734</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>615944</t>
+          <t>616032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>707517</t>
+          <t>708213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>724461</t>
+          <t>725055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1318107</t>
+          <t>1316907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337426</t>
+          <t>1337939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -9864,97 +9864,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6683</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1898</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>7379</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>7426</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1898</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26696</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275925</t>
+          <t>275799</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>283000</t>
+          <t>283005</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1050435</t>
+          <t>1050891</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1067780</t>
+          <t>1067072</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1330548</t>
+          <t>1330775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1349871</t>
+          <t>1349665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10340,77 +10340,77 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>18690</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>11567</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>27985</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>20708</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>12769</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>31076</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>18690</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>11424</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>27565</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>20708</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>12226</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>30335</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42350</t>
+          <t>42084</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87460</t>
+          <t>87787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126747</t>
+          <t>128523</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>114473</t>
+          <t>116771</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>158928</t>
+          <t>162266</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3326895</t>
+          <t>3326544</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3349174</t>
+          <t>3348551</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3372179</t>
+          <t>3368841</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3413580</t>
+          <t>3413872</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6707680</t>
+          <t>6706029</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6756503</t>
+          <t>6755093</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23697</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51098</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>39314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68923</t>
+          <t>67830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>445957</t>
+          <t>446801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>464435</t>
+          <t>464052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251806</t>
+          <t>253481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>276864</t>
+          <t>277135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>703943</t>
+          <t>705516</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>736998</t>
+          <t>736117</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78640</t>
+          <t>79011</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51450</t>
+          <t>49268</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83792</t>
+          <t>79984</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>358891</t>
+          <t>357897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366056</t>
+          <t>366051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>286596</t>
+          <t>285230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317557</t>
+          <t>316039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>648425</t>
+          <t>650613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>680363</t>
+          <t>682254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17347</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>39314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522298</t>
+          <t>520632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>535886</t>
+          <t>535824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140143</t>
+          <t>139070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156279</t>
+          <t>156120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667687</t>
+          <t>666133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>688376</t>
+          <t>688925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27161</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75335</t>
+          <t>74492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59514</t>
+          <t>58720</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91884</t>
+          <t>93387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1204406</t>
+          <t>1206121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1224755</t>
+          <t>1225307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>638003</t>
+          <t>638388</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>668169</t>
+          <t>668400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1854937</t>
+          <t>1853535</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1888583</t>
+          <t>1889007</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38882</t>
+          <t>39629</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>335601</t>
+          <t>335102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>347032</t>
+          <t>347380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>529870</t>
+          <t>529123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>550960</t>
+          <t>550721</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>872573</t>
+          <t>872104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>896009</t>
+          <t>896747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36411</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>63957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39903</t>
+          <t>40873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67868</t>
+          <t>69092</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>288404</t>
+          <t>288586</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297180</t>
+          <t>297200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1185644</t>
+          <t>1184803</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1212349</t>
+          <t>1211200</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1479092</t>
+          <t>1477868</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1507057</t>
+          <t>1506087</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20502</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,44 +3488,44 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>12483</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>6953</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>21444</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>12483</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6507</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>21001</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>42311</t>
+          <t>42020</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72492</t>
+          <t>73584</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>218753</t>
+          <t>224119</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>279406</t>
+          <t>284066</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>274090</t>
+          <t>275988</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>344682</t>
+          <t>342432</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3184979</t>
+          <t>3185551</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3218652</t>
+          <t>3220629</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3084917</t>
+          <t>3079462</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3146755</t>
+          <t>3141609</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6278516</t>
+          <t>6283275</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6354629</t>
+          <t>6351130</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53547</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72828</t>
+          <t>71561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>408966</t>
+          <t>409683</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>427262</t>
+          <t>426802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253250</t>
+          <t>253330</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>280880</t>
+          <t>281743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>670366</t>
+          <t>670709</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>704351</t>
+          <t>704322</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>32146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57675</t>
+          <t>57446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71317</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>398781</t>
+          <t>400833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>412565</t>
+          <t>412736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>274094</t>
+          <t>273313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>300827</t>
+          <t>300044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>677715</t>
+          <t>679527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>709206</t>
+          <t>709646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23700</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>48352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598294</t>
+          <t>597634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>615036</t>
+          <t>614433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221145</t>
+          <t>221428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241742</t>
+          <t>241421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>823409</t>
+          <t>825660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>852399</t>
+          <t>853286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t>39224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74805</t>
+          <t>74727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70168</t>
+          <t>66637</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106653</t>
+          <t>104600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1109382</t>
+          <t>1109948</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1132076</t>
+          <t>1133569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>685201</t>
+          <t>685428</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>715519</t>
+          <t>714439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1802416</t>
+          <t>1804152</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1839361</t>
+          <t>1842242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>40045</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>497658</t>
+          <t>496160</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>508525</t>
+          <t>508205</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>717521</t>
+          <t>718164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>738389</t>
+          <t>739021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1220358</t>
+          <t>1221171</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1244667</t>
+          <t>1244240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>34888</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60097</t>
+          <t>60693</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68643</t>
+          <t>67409</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>254355</t>
+          <t>254258</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264606</t>
+          <t>264826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1039086</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1066474</t>
+          <t>1065949</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1296411</t>
+          <t>1298280</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1328195</t>
+          <t>1328098</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,82 +6909,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>32967</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>21542</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>44238</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>40183</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>28600</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>54634</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>32967</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>21994</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>47376</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>40183</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>29200</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>55620</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>61985</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>98089</t>
+          <t>99029</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>198592</t>
+          <t>199725</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>261476</t>
+          <t>259072</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>273873</t>
+          <t>272507</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>341665</t>
+          <t>340758</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3302293</t>
+          <t>3303296</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3339306</t>
+          <t>3340785</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3238471</t>
+          <t>3242471</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3307382</t>
+          <t>3304971</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6559894</t>
+          <t>6560837</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6634171</t>
+          <t>6634359</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>419707</t>
+          <t>420023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>428085</t>
+          <t>428081</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>323459</t>
+          <t>322382</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>339173</t>
+          <t>339021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>747325</t>
+          <t>747606</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>764570</t>
+          <t>764432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22246</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362982</t>
+          <t>362934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>346290</t>
+          <t>347406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>361408</t>
+          <t>362255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>714426</t>
+          <t>713632</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>730329</t>
+          <t>729851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>510801</t>
+          <t>510480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>519803</t>
+          <t>519799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147818</t>
+          <t>147599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159774</t>
+          <t>159743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>663236</t>
+          <t>662848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>678076</t>
+          <t>678205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30441</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>57342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40680</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>69414</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1128439</t>
+          <t>1128349</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1141867</t>
+          <t>1141667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>759079</t>
+          <t>757103</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>785308</t>
+          <t>784822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1893308</t>
+          <t>1891358</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1923050</t>
+          <t>1922563</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>604734</t>
+          <t>604441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>616032</t>
+          <t>616078</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>708213</t>
+          <t>707016</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>725055</t>
+          <t>724524</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1316907</t>
+          <t>1318267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337939</t>
+          <t>1338157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27581</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275799</t>
+          <t>275630</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1050891</t>
+          <t>1051471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1067072</t>
+          <t>1068369</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1330775</t>
+          <t>1330201</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1349665</t>
+          <t>1349147</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27985</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87787</t>
+          <t>88477</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>127397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>116771</t>
+          <t>115368</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>162266</t>
+          <t>161188</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3326544</t>
+          <t>3327157</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3348551</t>
+          <t>3349386</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3368841</t>
+          <t>3371056</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3413872</t>
+          <t>3412035</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6706029</t>
+          <t>6707858</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6755093</t>
+          <t>6757032</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
